--- a/data/trans_dic/IP2907_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP2907_2023-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que durante sus primeros meses de vida recibiero unicamente lactancia artificial</t>
+          <t>Menores que durante sus primeros meses de vida recibiero unicamente lactancia artificial (tasa de respuesta: 98,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,27; 21,45</t>
+          <t>6,09; 20,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,96; 30,99</t>
+          <t>12,28; 31,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,86; 22,92</t>
+          <t>10,74; 23,21</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,85; 24,8</t>
+          <t>17,65; 24,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,13; 24,28</t>
+          <t>16,18; 24,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,78; 22,95</t>
+          <t>17,71; 23,01</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,79; 21,46</t>
+          <t>12,0; 22,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,09; 25,77</t>
+          <t>15,26; 25,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,85; 22,43</t>
+          <t>15,22; 22,46</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,53; 22,01</t>
+          <t>16,38; 21,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,02; 23,25</t>
+          <t>16,96; 23,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,44; 21,59</t>
+          <t>17,5; 21,85</t>
         </is>
       </c>
     </row>
@@ -752,4 +753,380 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que durante sus primeros meses de vida recibiero unicamente lactancia artificial (tasa de respuesta: 98,6%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>6475</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11681</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18155</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>3222; 10984</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7090; 18244</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11882; 25675</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>87674</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>98230</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>185903</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>74100; 102573</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>81024; 123013</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>163103; 211906</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>23277</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>35997</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>59274</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>17141; 32148</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27263; 46389</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>48935; 72185</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>117425</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>145907</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>263332</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>100839; 134116</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>125043; 172695</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>236734; 295564</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2907_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP2907_2023-Estudios-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,09; 20,78</t>
+          <t>5,98; 20,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,28; 31,59</t>
+          <t>11,95; 29,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,74; 23,21</t>
+          <t>11,0; 23,1</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,65; 24,43</t>
+          <t>17,75; 24,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,18; 24,56</t>
+          <t>15,89; 24,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,71; 23,01</t>
+          <t>17,54; 22,86</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,0; 22,51</t>
+          <t>11,64; 21,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,26; 25,97</t>
+          <t>15,14; 26,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,22; 22,46</t>
+          <t>15,04; 22,79</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,38; 21,79</t>
+          <t>16,31; 21,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,96; 23,42</t>
+          <t>17,17; 23,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,5; 21,85</t>
+          <t>17,5; 21,71</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3222; 10984</t>
+          <t>3160; 10957</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7090; 18244</t>
+          <t>6901; 17151</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11882; 25675</t>
+          <t>12167; 25556</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>74100; 102573</t>
+          <t>74537; 102534</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>81024; 123013</t>
+          <t>79609; 120643</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>163103; 211906</t>
+          <t>161532; 210501</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17141; 32148</t>
+          <t>16630; 31033</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27263; 46389</t>
+          <t>27046; 46855</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48935; 72185</t>
+          <t>48353; 73264</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>100839; 134116</t>
+          <t>100375; 135129</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>125043; 172695</t>
+          <t>126570; 171111</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>236734; 295564</t>
+          <t>236704; 293704</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2907_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP2907_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,98; 20,73</t>
+          <t>11,87; 31,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,95; 29,7</t>
+          <t>7,22; 22,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,0; 23,1</t>
+          <t>11,9; 23,95</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,75; 24,42</t>
+          <t>15,5; 22,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,89; 24,09</t>
+          <t>17,98; 24,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,54; 22,86</t>
+          <t>17,44; 22,47</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,64; 21,73</t>
+          <t>15,39; 26,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,14; 26,23</t>
+          <t>11,42; 20,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,04; 22,79</t>
+          <t>14,49; 22,03</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,31; 21,95</t>
+          <t>16,43; 22,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,17; 23,21</t>
+          <t>16,6; 22,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,5; 21,71</t>
+          <t>17,24; 21,21</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11681</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18155</t>
+          <t>16956</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3160; 10957</t>
+          <t>6305; 16647</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6901; 17151</t>
+          <t>3249; 10355</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12167; 25556</t>
+          <t>11681; 23506</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>132</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>87674</t>
+          <t>86574</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>98230</t>
+          <t>87520</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>185903</t>
+          <t>174094</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>74537; 102534</t>
+          <t>71632; 105204</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79609; 120643</t>
+          <t>74785; 103483</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>161532; 210501</t>
+          <t>153128; 197301</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>35</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23277</t>
+          <t>33420</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35997</t>
+          <t>22484</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59274</t>
+          <t>55904</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16630; 31033</t>
+          <t>25279; 42751</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27046; 46855</t>
+          <t>16396; 29708</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48353; 73264</t>
+          <t>44596; 67814</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>178</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>117425</t>
+          <t>130749</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>145907</t>
+          <t>116204</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>263332</t>
+          <t>246953</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>100375; 135129</t>
+          <t>111678; 150256</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>126570; 171111</t>
+          <t>100342; 134235</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>236704; 293704</t>
+          <t>221356; 272415</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2907_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP2907_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que durante sus primeros meses de vida recibiero unicamente lactancia artificial (tasa de respuesta: 98,6%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>20,25%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13,77%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17,27%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>11,87; 31,34</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>7,22; 22,99</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11,9; 23,95</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>18,73%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>21,04%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>19,82%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>15,5; 22,76</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>17,98; 24,88</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>17,44; 22,47</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>20,35%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>15,66%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>18,16%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>15,39; 26,03</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>11,42; 20,69</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>14,49; 22,03</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>19,24%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>19,22%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>19,23%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>16,43; 22,11</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>16,6; 22,2</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>17,24; 21,21</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.202463935088152</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.137683916143143</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.1727421612895238</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>10755</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>6201</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16956</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.1186892974070932</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.07215467571271807</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.1190066383340316</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>6305; 16647</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3249; 10355</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>11681; 23506</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.3133783258917565</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.229939600869586</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.2394795012487162</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.187310895451468</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.2103796296843336</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.1982386392115853</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>86574</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>87520</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>174094</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.1549823015964394</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.179768989319184</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.1743653677204688</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>71632; 105204</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>74785; 103483</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>153128; 197301</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.2276190475697958</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.2487523643452332</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.2246651091480751</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.2034503839629952</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1566194823265644</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.181609858919709</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>33420</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>22484</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>55904</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.1538902510094122</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.1142111582552067</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.1448729221574557</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>25279; 42751</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>16396; 29708</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>44596; 67814</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.2602569892399154</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.2069358025084114</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.2202991126521049</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1923965303494996</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1921996255507721</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1923038261121431</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>130749</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>116204</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>246953</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.1643337802569707</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.1659640783710174</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.1723708856581548</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>111678; 150256</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>100342; 134235</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>221356; 272415</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.221101438407431</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.2220210924656818</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.2121309887623949</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que durante sus primeros meses de vida recibiero unicamente lactancia artificial (tasa de respuesta: 98,6%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>10755</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>6201</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>16956</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>6305</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>3249</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>11681</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>16647</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>10355</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>23506</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>113</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>86574</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>87520</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>174094</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>71632</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>74785</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>153128</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>105204</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>103483</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>197301</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>33420</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>22484</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>55904</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>25279</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>16396</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>44596</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>42751</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>29708</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>67814</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>179</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>178</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>130749</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>116204</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>246953</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>111678</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>100342</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>221356</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>150256</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>134235</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>272415</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>